--- a/documents/sales.xlsx
+++ b/documents/sales.xlsx
@@ -516,7 +516,6 @@
           <t>2023-12-01</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>75000</v>
       </c>
@@ -568,7 +567,6 @@
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>94900</v>
       </c>
@@ -620,7 +618,6 @@
           <t>2020-01-28</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>100100</v>
       </c>
@@ -672,7 +669,6 @@
           <t>2025-03-28</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>74600</v>
       </c>
@@ -724,7 +720,6 @@
           <t>2022-10-23</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>118500</v>
       </c>
@@ -776,7 +771,6 @@
           <t>2023-09-02</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>101000</v>
       </c>
@@ -828,7 +822,6 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>120100</v>
       </c>
@@ -880,7 +873,6 @@
           <t>2022-10-15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>104300</v>
       </c>
@@ -932,7 +924,6 @@
           <t>2023-12-09</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>84600</v>
       </c>
@@ -984,7 +975,6 @@
           <t>2024-01-25</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>124700</v>
       </c>
@@ -1036,7 +1026,6 @@
           <t>2022-10-08</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>103500</v>
       </c>
@@ -1088,7 +1077,6 @@
           <t>2023-05-02</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>64400</v>
       </c>
@@ -1140,7 +1128,6 @@
           <t>2023-10-01</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>67100</v>
       </c>
@@ -1192,7 +1179,6 @@
           <t>2024-08-20</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>70000</v>
       </c>
@@ -1244,7 +1230,6 @@
           <t>2019-11-09</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>124700</v>
       </c>
@@ -1296,7 +1281,6 @@
           <t>2023-06-21</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>107400</v>
       </c>
@@ -1348,7 +1332,6 @@
           <t>2022-03-03</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>81000</v>
       </c>
@@ -1400,7 +1383,6 @@
           <t>2024-03-10</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>86000</v>
       </c>
@@ -1452,7 +1434,6 @@
           <t>2021-03-24</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>143500</v>
       </c>
@@ -1504,7 +1485,6 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>88700</v>
       </c>
@@ -1556,7 +1536,6 @@
           <t>2020-03-15</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>127500</v>
       </c>
@@ -1608,7 +1587,6 @@
           <t>2025-10-20</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>91000</v>
       </c>
@@ -1660,7 +1638,6 @@
           <t>2024-01-07</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>105000</v>
       </c>
@@ -1712,7 +1689,6 @@
           <t>2025-07-18</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>120000</v>
       </c>
@@ -1764,7 +1740,6 @@
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>79300</v>
       </c>
@@ -1816,7 +1791,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>70600</v>
       </c>
@@ -1868,7 +1842,6 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>106500</v>
       </c>
@@ -1920,7 +1893,6 @@
           <t>2023-11-10</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>135000</v>
       </c>
@@ -1972,7 +1944,6 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>109100</v>
       </c>
@@ -2024,7 +1995,6 @@
           <t>2019-12-08</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>77600</v>
       </c>
@@ -2076,7 +2046,6 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
         <v>80800</v>
       </c>
@@ -2128,7 +2097,6 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>92800</v>
       </c>
@@ -2180,7 +2148,6 @@
           <t>2018-10-03</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
         <v>119800</v>
       </c>
@@ -2232,7 +2199,6 @@
           <t>2019-02-23</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
         <v>89700</v>
       </c>
@@ -2284,7 +2250,6 @@
           <t>2021-03-25</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
         <v>78700</v>
       </c>
@@ -2336,7 +2301,6 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>94200</v>
       </c>
@@ -2388,7 +2352,6 @@
           <t>2025-01-02</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>87000</v>
       </c>
@@ -2440,7 +2403,6 @@
           <t>2023-10-03</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>90700</v>
       </c>
@@ -2492,7 +2454,6 @@
           <t>2020-05-20</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>102400</v>
       </c>
@@ -2544,7 +2505,6 @@
           <t>2021-12-14</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
         <v>92000</v>
       </c>
@@ -2596,7 +2556,6 @@
           <t>2022-07-17</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
         <v>91100</v>
       </c>
@@ -2648,7 +2607,6 @@
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>86500</v>
       </c>
@@ -2700,7 +2658,6 @@
           <t>2024-02-13</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
         <v>88200</v>
       </c>
@@ -2752,7 +2709,6 @@
           <t>2023-05-14</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
         <v>97200</v>
       </c>
@@ -2804,7 +2760,6 @@
           <t>2021-08-12</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
         <v>70400</v>
       </c>
@@ -2856,7 +2811,6 @@
           <t>2025-10-22</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
         <v>72100</v>
       </c>
@@ -2908,7 +2862,6 @@
           <t>2023-04-24</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
         <v>105400</v>
       </c>
@@ -2960,7 +2913,6 @@
           <t>2022-01-09</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
         <v>79600</v>
       </c>
@@ -3012,7 +2964,6 @@
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
         <v>90000</v>
       </c>
@@ -3064,7 +3015,6 @@
           <t>2025-02-07</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
         <v>110500</v>
       </c>
@@ -3116,7 +3066,6 @@
           <t>2024-01-16</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
         <v>70700</v>
       </c>
@@ -3168,7 +3117,6 @@
           <t>2025-03-25</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
         <v>90700</v>
       </c>
@@ -3220,7 +3168,6 @@
           <t>2020-04-14</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
         <v>95000</v>
       </c>
@@ -3272,7 +3219,6 @@
           <t>2023-11-04</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
         <v>69100</v>
       </c>
@@ -3324,7 +3270,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
         <v>75400</v>
       </c>
@@ -3376,7 +3321,6 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
         <v>107900</v>
       </c>
@@ -3428,7 +3372,6 @@
           <t>2024-06-26</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
         <v>82000</v>
       </c>
@@ -3480,7 +3423,6 @@
           <t>2024-02-11</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
         <v>73400</v>
       </c>
@@ -3532,7 +3474,6 @@
           <t>2025-02-27</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
         <v>79800</v>
       </c>
@@ -3584,7 +3525,6 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>80300</v>
       </c>
@@ -3636,7 +3576,6 @@
           <t>2022-11-25</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>103900</v>
       </c>
@@ -3688,7 +3627,6 @@
           <t>2024-07-19</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
         <v>85800</v>
       </c>
@@ -3740,7 +3678,6 @@
           <t>2022-07-14</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
         <v>64400</v>
       </c>
@@ -3792,7 +3729,6 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
         <v>77400</v>
       </c>
@@ -3844,7 +3780,6 @@
           <t>2025-11-11</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
         <v>87100</v>
       </c>
@@ -3896,7 +3831,6 @@
           <t>2025-02-27</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
         <v>67100</v>
       </c>
@@ -3948,7 +3882,6 @@
           <t>2023-11-15</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
         <v>82800</v>
       </c>
@@ -4000,7 +3933,6 @@
           <t>2023-07-26</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
         <v>92800</v>
       </c>
@@ -4052,7 +3984,6 @@
           <t>2020-05-10</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
         <v>84700</v>
       </c>
@@ -4104,7 +4035,6 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
         <v>81300</v>
       </c>
@@ -4156,7 +4086,6 @@
           <t>2023-05-13</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
         <v>92500</v>
       </c>
@@ -4208,7 +4137,6 @@
           <t>2022-05-04</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
         <v>118000</v>
       </c>
@@ -4260,7 +4188,6 @@
           <t>2023-07-12</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
         <v>68400</v>
       </c>
@@ -4312,7 +4239,6 @@
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
         <v>113000</v>
       </c>
@@ -4364,7 +4290,6 @@
           <t>2022-06-20</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
         <v>69900</v>
       </c>
@@ -4416,7 +4341,6 @@
           <t>2022-10-20</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
         <v>96700</v>
       </c>
@@ -4468,7 +4392,6 @@
           <t>2023-09-03</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
         <v>121100</v>
       </c>
@@ -4520,7 +4443,6 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>97100</v>
       </c>
@@ -4572,7 +4494,6 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
         <v>104100</v>
       </c>
@@ -4624,7 +4545,6 @@
           <t>2024-12-18</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>95600</v>
       </c>
@@ -4676,7 +4596,6 @@
           <t>2023-10-21</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>102000</v>
       </c>
@@ -4728,7 +4647,6 @@
           <t>2024-11-22</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>61100</v>
       </c>
@@ -4780,7 +4698,6 @@
           <t>2019-09-19</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
         <v>104400</v>
       </c>
@@ -4832,7 +4749,6 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
         <v>97500</v>
       </c>
@@ -4884,7 +4800,6 @@
           <t>2023-10-05</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>96300</v>
       </c>
@@ -4936,7 +4851,6 @@
           <t>2019-02-18</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
         <v>91700</v>
       </c>
@@ -4988,7 +4902,6 @@
           <t>2023-05-13</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
         <v>119000</v>
       </c>
@@ -5040,7 +4953,6 @@
           <t>2025-05-02</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
         <v>76600</v>
       </c>
@@ -5092,7 +5004,6 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
         <v>81700</v>
       </c>
@@ -5144,7 +5055,6 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
         <v>116400</v>
       </c>
@@ -5196,7 +5106,6 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
         <v>101400</v>
       </c>
@@ -5248,7 +5157,6 @@
           <t>2020-01-08</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
         <v>103300</v>
       </c>
@@ -5300,7 +5208,6 @@
           <t>2022-12-23</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
         <v>126900</v>
       </c>
@@ -5352,7 +5259,6 @@
           <t>2023-11-20</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
         <v>104600</v>
       </c>
@@ -5404,7 +5310,6 @@
           <t>2023-08-16</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>113400</v>
       </c>
@@ -5456,7 +5361,6 @@
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>78800</v>
       </c>
@@ -5508,7 +5412,6 @@
           <t>2023-02-02</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
         <v>106700</v>
       </c>
@@ -5560,7 +5463,6 @@
           <t>2023-09-02</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
         <v>77800</v>
       </c>
@@ -5612,7 +5514,6 @@
           <t>2022-11-26</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>79300</v>
       </c>
@@ -5664,7 +5565,6 @@
           <t>2024-03-16</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
         <v>76000</v>
       </c>
@@ -5716,7 +5616,6 @@
           <t>2022-03-04</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
         <v>65800</v>
       </c>
@@ -5768,7 +5667,6 @@
           <t>2024-12-13</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
         <v>71700</v>
       </c>
@@ -5820,7 +5718,6 @@
           <t>2023-02-06</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
         <v>86900</v>
       </c>
@@ -5872,7 +5769,6 @@
           <t>2023-03-25</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
         <v>76300</v>
       </c>
@@ -5924,7 +5820,6 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
         <v>89100</v>
       </c>
@@ -5976,7 +5871,6 @@
           <t>2025-01-25</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
         <v>80800</v>
       </c>
@@ -6028,7 +5922,6 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
         <v>81900</v>
       </c>
@@ -6080,7 +5973,6 @@
           <t>2025-01-16</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
         <v>74800</v>
       </c>
@@ -6132,7 +6024,6 @@
           <t>2024-05-14</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
         <v>70500</v>
       </c>
@@ -6184,7 +6075,6 @@
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
         <v>83500</v>
       </c>
@@ -6236,7 +6126,6 @@
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
         <v>105500</v>
       </c>
@@ -6288,7 +6177,6 @@
           <t>2024-06-14</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
         <v>75500</v>
       </c>
@@ -6340,7 +6228,6 @@
           <t>2021-12-05</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
         <v>88700</v>
       </c>
@@ -6392,7 +6279,6 @@
           <t>2023-04-15</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
         <v>87700</v>
       </c>
@@ -6444,7 +6330,6 @@
           <t>2021-07-07</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="n">
         <v>99500</v>
       </c>
@@ -6496,7 +6381,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
         <v>122800</v>
       </c>
@@ -6548,7 +6432,6 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
         <v>83100</v>
       </c>
@@ -6600,7 +6483,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
         <v>96100</v>
       </c>
@@ -6652,7 +6534,6 @@
           <t>2022-08-10</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
         <v>86300</v>
       </c>
@@ -6704,7 +6585,6 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
         <v>76400</v>
       </c>
@@ -6756,7 +6636,6 @@
           <t>2023-02-04</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
         <v>97300</v>
       </c>
@@ -6808,7 +6687,6 @@
           <t>2024-03-07</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
         <v>80300</v>
       </c>
@@ -6860,7 +6738,6 @@
           <t>2019-08-28</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
         <v>79300</v>
       </c>
@@ -6912,7 +6789,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
         <v>70900</v>
       </c>
@@ -6964,7 +6840,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
         <v>67600</v>
       </c>
@@ -7082,7 +6957,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -7138,7 +7013,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -7250,7 +7125,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -7306,7 +7181,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -7362,7 +7237,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -7418,7 +7293,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -7530,7 +7405,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -7586,7 +7461,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -7744,7 +7619,6 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
         <v>85500</v>
       </c>
@@ -7862,7 +7736,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -8086,7 +7960,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -8254,7 +8128,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -8310,7 +8184,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -8366,7 +8240,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I151" t="n">
@@ -8478,7 +8352,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -8814,7 +8688,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -8870,7 +8744,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I160" t="n">
@@ -8982,7 +8856,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -9150,7 +9024,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I165" t="n">
@@ -9318,7 +9192,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I168" t="n">
@@ -9710,7 +9584,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -9822,7 +9696,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I177" t="n">
@@ -9868,7 +9742,6 @@
           <t>2024-08-23</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
         <v>89100</v>
       </c>
@@ -9986,7 +9859,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -10042,7 +9915,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -10322,7 +10195,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -10480,7 +10353,6 @@
           <t>2024-03-08</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
         <v>92300</v>
       </c>
@@ -10822,7 +10694,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I195" t="n">
@@ -10868,7 +10740,6 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
       <c r="G196" t="n">
         <v>130500</v>
       </c>
@@ -11322,7 +11193,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -11378,7 +11249,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I205" t="n">
@@ -11546,7 +11417,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I208" t="n">
@@ -11602,7 +11473,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I209" t="n">
@@ -11714,7 +11585,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I211" t="n">
@@ -12106,7 +11977,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I218" t="n">
@@ -12218,7 +12089,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I220" t="n">
@@ -12442,7 +12313,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I224" t="n">
@@ -12498,7 +12369,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I225" t="n">
@@ -12554,7 +12425,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I226" t="n">
@@ -12722,7 +12593,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I229" t="n">
@@ -12890,7 +12761,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I232" t="n">
@@ -13058,7 +12929,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I235" t="n">
@@ -13114,7 +12985,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I236" t="n">
@@ -13506,7 +13377,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I243" t="n">
@@ -13562,7 +13433,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I244" t="n">
@@ -13786,7 +13657,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I248" t="n">
@@ -13954,7 +13825,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I251" t="n">
@@ -14066,7 +13937,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I253" t="n">
@@ -14290,7 +14161,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I257" t="n">
@@ -14346,7 +14217,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I258" t="n">
@@ -14850,7 +14721,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I267" t="n">
@@ -14896,7 +14767,6 @@
           <t>2023-05-20</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr"/>
       <c r="G268" t="n">
         <v>84900</v>
       </c>
@@ -15238,7 +15108,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I274" t="n">
@@ -15462,7 +15332,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I278" t="n">
@@ -15630,7 +15500,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I281" t="n">
@@ -15686,7 +15556,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I282" t="n">
@@ -15798,7 +15668,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I284" t="n">
@@ -15966,7 +15836,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I287" t="n">
@@ -16022,7 +15892,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I288" t="n">
@@ -16078,7 +15948,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I289" t="n">
@@ -16190,7 +16060,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I291" t="n">
@@ -16470,7 +16340,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I296" t="n">
@@ -16526,7 +16396,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I297" t="n">
@@ -16582,7 +16452,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I298" t="n">
@@ -16694,7 +16564,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I300" t="n">
@@ -16974,7 +16844,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I305" t="n">
@@ -17198,7 +17068,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I309" t="n">
@@ -17422,7 +17292,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I313" t="n">
@@ -17478,7 +17348,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I314" t="n">
@@ -17534,7 +17404,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I315" t="n">
@@ -17702,7 +17572,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I318" t="n">
@@ -17758,7 +17628,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I319" t="n">
@@ -17814,7 +17684,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I320" t="n">
@@ -17926,7 +17796,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I322" t="n">
@@ -18262,7 +18132,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I328" t="n">
@@ -18430,7 +18300,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I331" t="n">
@@ -18486,7 +18356,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I332" t="n">
@@ -18644,7 +18514,6 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr"/>
       <c r="G335" t="n">
         <v>82600</v>
       </c>
@@ -18706,7 +18575,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I336" t="n">
@@ -18762,7 +18631,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I337" t="n">
@@ -19098,7 +18967,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I343" t="n">
@@ -19210,7 +19079,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I345" t="n">

--- a/documents/sales.xlsx
+++ b/documents/sales.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L346"/>
+  <dimension ref="A1:L357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,12 +567,17 @@
           <t>2026-02-15</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="G3" t="n">
         <v>94900</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -873,12 +878,17 @@
           <t>2022-10-15</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
       <c r="G9" t="n">
         <v>104300</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1128,12 +1138,17 @@
           <t>2023-10-01</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
       <c r="G14" t="n">
         <v>67100</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1179,12 +1194,17 @@
           <t>2024-08-20</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="G15" t="n">
         <v>70000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1332,12 +1352,17 @@
           <t>2022-03-03</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="G18" t="n">
         <v>81000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1434,12 +1459,17 @@
           <t>2021-03-24</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
       <c r="G20" t="n">
         <v>143500</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1536,12 +1566,17 @@
           <t>2020-03-15</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
       <c r="G22" t="n">
         <v>127500</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -2250,12 +2285,17 @@
           <t>2021-03-25</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="G36" t="n">
         <v>78700</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2352,12 +2392,17 @@
           <t>2025-01-02</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
       <c r="G38" t="n">
         <v>87000</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2505,12 +2550,17 @@
           <t>2021-12-14</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
       <c r="G41" t="n">
         <v>92000</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2862,12 +2912,17 @@
           <t>2023-04-24</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="G48" t="n">
         <v>105400</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3780,12 +3835,17 @@
           <t>2025-11-11</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
       <c r="G66" t="n">
         <v>87100</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4137,12 +4197,17 @@
           <t>2022-05-04</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="G73" t="n">
         <v>118000</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4239,12 +4304,17 @@
           <t>2023-05-22</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="G75" t="n">
         <v>113000</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4290,12 +4360,17 @@
           <t>2022-06-20</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
       <c r="G76" t="n">
         <v>69900</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4341,12 +4416,17 @@
           <t>2022-10-20</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
       <c r="G77" t="n">
         <v>96700</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4494,12 +4574,17 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
       <c r="G80" t="n">
         <v>104100</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4902,12 +4987,17 @@
           <t>2023-05-13</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="G88" t="n">
         <v>119000</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -5310,12 +5400,17 @@
           <t>2023-08-16</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
       <c r="G96" t="n">
         <v>113400</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -5718,12 +5813,17 @@
           <t>2023-02-06</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
       <c r="G104" t="n">
         <v>86900</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5820,12 +5920,17 @@
           <t>2021-07-01</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
       <c r="G106" t="n">
         <v>89100</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -6024,12 +6129,17 @@
           <t>2024-05-14</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="G110" t="n">
         <v>70500</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -6636,12 +6746,17 @@
           <t>2023-02-04</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="G122" t="n">
         <v>97300</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -19150,6 +19265,567 @@
         </is>
       </c>
       <c r="L346" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Deborah Stewart</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>1997-09-19</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Senior AE</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G347" t="n">
+        <v>91200</v>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I347" t="n">
+        <v>0</v>
+      </c>
+      <c r="J347" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Peter Smith</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>1990-04-22</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G348" t="n">
+        <v>76900</v>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I348" t="n">
+        <v>3</v>
+      </c>
+      <c r="J348" t="n">
+        <v>7</v>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Emma Phillips</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>1981-03-27</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Regional Director</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>117100</v>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I349" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Dorothy Howard</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>1984-09-15</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G350" t="n">
+        <v>87900</v>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I350" t="n">
+        <v>2</v>
+      </c>
+      <c r="J350" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Henry Gutierrez</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>1999-11-22</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G351" t="n">
+        <v>65700</v>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I351" t="n">
+        <v>3</v>
+      </c>
+      <c r="J351" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Susan Kim</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>1976-04-22</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G352" t="n">
+        <v>126800</v>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I352" t="n">
+        <v>2</v>
+      </c>
+      <c r="J352" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Diana Kelly</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2001-09-05</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G353" t="n">
+        <v>98200</v>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I353" t="n">
+        <v>1</v>
+      </c>
+      <c r="J353" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Frank Wood</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>1989-08-27</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G354" t="n">
+        <v>70700</v>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I354" t="n">
+        <v>3</v>
+      </c>
+      <c r="J354" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Stephanie Ward</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>1982-11-02</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G355" t="n">
+        <v>107300</v>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I355" t="n">
+        <v>3</v>
+      </c>
+      <c r="J355" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Nicole Phillips</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>1976-11-28</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G356" t="n">
+        <v>76000</v>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I356" t="n">
+        <v>3</v>
+      </c>
+      <c r="J356" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Danielle Wallace</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>1969-06-07</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G357" t="n">
+        <v>80400</v>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I357" t="n">
+        <v>3</v>
+      </c>
+      <c r="J357" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
         <is>
           <t>White</t>
         </is>
